--- a/tests/fixtures/tne_planted/data/Attendee_Validity_Report.xlsx
+++ b/tests/fixtures/tne_planted/data/Attendee_Validity_Report.xlsx
@@ -724,42 +724,42 @@
     <t>T61C Report 50033</t>
   </si>
   <si>
+    <t>Haddad, Omar</t>
+  </si>
+  <si>
+    <t>Alvarez, Diego</t>
+  </si>
+  <si>
+    <t>Costa, Bruno</t>
+  </si>
+  <si>
+    <t>Wong, Kelly</t>
+  </si>
+  <si>
+    <t>Singh, Manpreet</t>
+  </si>
+  <si>
+    <t>Novak, Petra</t>
+  </si>
+  <si>
+    <t>Fischer, Lena</t>
+  </si>
+  <si>
     <t>Patel, Nisha</t>
   </si>
   <si>
-    <t>Alvarez, Diego</t>
-  </si>
-  <si>
-    <t>Fischer, Lena</t>
+    <t>Dubois, Camille</t>
+  </si>
+  <si>
+    <t>Larsen, Freya</t>
   </si>
   <si>
     <t>Ibrahim, Yusuf</t>
   </si>
   <si>
-    <t>Costa, Bruno</t>
-  </si>
-  <si>
-    <t>Haddad, Omar</t>
-  </si>
-  <si>
-    <t>Dubois, Camille</t>
-  </si>
-  <si>
-    <t>Novak, Petra</t>
-  </si>
-  <si>
     <t>Osei, Kwame</t>
   </si>
   <si>
-    <t>Wong, Kelly</t>
-  </si>
-  <si>
-    <t>Singh, Manpreet</t>
-  </si>
-  <si>
-    <t>Larsen, Freya</t>
-  </si>
-  <si>
     <t>Guest, One</t>
   </si>
   <si>
@@ -781,19 +781,19 @@
     <t>Corner Cafe</t>
   </si>
   <si>
+    <t>Officeworks</t>
+  </si>
+  <si>
+    <t>Ampol Fuel</t>
+  </si>
+  <si>
     <t>Wilson Parking</t>
   </si>
   <si>
     <t>Telstra Corp</t>
   </si>
   <si>
-    <t>Officeworks</t>
-  </si>
-  <si>
     <t>City Cabs</t>
-  </si>
-  <si>
-    <t>Ampol Fuel</t>
   </si>
   <si>
     <t>Harbour Restaurant</t>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>90010</v>
+        <v>90012</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -1424,7 +1424,7 @@
         <v>254</v>
       </c>
       <c r="F2" s="1">
-        <v>45713</v>
+        <v>46064</v>
       </c>
       <c r="G2" t="s">
         <v>333</v>
@@ -1433,7 +1433,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>25.3</v>
+        <v>44.35</v>
       </c>
       <c r="J2">
         <v>500000</v>
@@ -1444,13 +1444,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>90004</v>
+        <v>90009</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D3" t="s">
         <v>250</v>
@@ -1459,7 +1459,7 @@
         <v>255</v>
       </c>
       <c r="F3" s="1">
-        <v>45968</v>
+        <v>45660</v>
       </c>
       <c r="G3" t="s">
         <v>333</v>
@@ -1468,7 +1468,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>35.49</v>
+        <v>59.13</v>
       </c>
       <c r="J3">
         <v>500001</v>
@@ -1479,13 +1479,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>90004</v>
+        <v>90011</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D4" t="s">
         <v>250</v>
@@ -1494,7 +1494,7 @@
         <v>256</v>
       </c>
       <c r="F4" s="1">
-        <v>46081</v>
+        <v>46006</v>
       </c>
       <c r="G4" t="s">
         <v>333</v>
@@ -1503,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>16.4</v>
+        <v>23.3</v>
       </c>
       <c r="J4">
         <v>500002</v>
@@ -1514,13 +1514,13 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>90003</v>
+        <v>90005</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D5" t="s">
         <v>250</v>
@@ -1529,7 +1529,7 @@
         <v>255</v>
       </c>
       <c r="F5" s="1">
-        <v>46126</v>
+        <v>45981</v>
       </c>
       <c r="G5" t="s">
         <v>333</v>
@@ -1538,7 +1538,7 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>53.63</v>
+        <v>32.85</v>
       </c>
       <c r="J5">
         <v>500003</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>90007</v>
+        <v>90003</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D6" t="s">
         <v>250</v>
@@ -1564,7 +1564,7 @@
         <v>257</v>
       </c>
       <c r="F6" s="1">
-        <v>45786</v>
+        <v>45925</v>
       </c>
       <c r="G6" t="s">
         <v>333</v>
@@ -1573,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>43.3</v>
+        <v>53.53</v>
       </c>
       <c r="J6">
         <v>500004</v>
@@ -1590,16 +1590,16 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D7" t="s">
         <v>250</v>
       </c>
       <c r="E7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F7" s="1">
-        <v>46052</v>
+        <v>45738</v>
       </c>
       <c r="G7" t="s">
         <v>333</v>
@@ -1608,7 +1608,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>51.39</v>
+        <v>22.25</v>
       </c>
       <c r="J7">
         <v>500005</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>90009</v>
+        <v>90003</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D8" t="s">
         <v>250</v>
       </c>
       <c r="E8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F8" s="1">
-        <v>46064</v>
+        <v>46037</v>
       </c>
       <c r="G8" t="s">
         <v>333</v>
@@ -1643,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>19.47</v>
+        <v>12.86</v>
       </c>
       <c r="J8">
         <v>500006</v>
@@ -1654,22 +1654,22 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>90008</v>
+        <v>90001</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D9" t="s">
         <v>250</v>
       </c>
       <c r="E9" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F9" s="1">
-        <v>45736</v>
+        <v>45702</v>
       </c>
       <c r="G9" t="s">
         <v>333</v>
@@ -1678,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>44.69</v>
+        <v>56.99</v>
       </c>
       <c r="J9">
         <v>500007</v>
@@ -1689,22 +1689,22 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>90012</v>
+        <v>90009</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D10" t="s">
         <v>250</v>
       </c>
       <c r="E10" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F10" s="1">
-        <v>46098</v>
+        <v>45983</v>
       </c>
       <c r="G10" t="s">
         <v>333</v>
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>42.9</v>
+        <v>11.7</v>
       </c>
       <c r="J10">
         <v>500008</v>
@@ -1724,19 +1724,19 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>90005</v>
+        <v>90004</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D11" t="s">
         <v>250</v>
       </c>
       <c r="E11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F11" s="1">
         <v>45792</v>
@@ -1748,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>59.81</v>
+        <v>11.01</v>
       </c>
       <c r="J11">
         <v>500009</v>
@@ -1765,16 +1765,16 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D12" t="s">
         <v>250</v>
       </c>
       <c r="E12" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F12" s="1">
-        <v>46043</v>
+        <v>45875</v>
       </c>
       <c r="G12" t="s">
         <v>333</v>
@@ -1783,7 +1783,7 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>59.21</v>
+        <v>50.01</v>
       </c>
       <c r="J12">
         <v>500010</v>
@@ -1794,22 +1794,22 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>90007</v>
+        <v>90010</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D13" t="s">
         <v>250</v>
       </c>
       <c r="E13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F13" s="1">
-        <v>45797</v>
+        <v>46014</v>
       </c>
       <c r="G13" t="s">
         <v>333</v>
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <v>55.89</v>
+        <v>49.18</v>
       </c>
       <c r="J13">
         <v>500011</v>
@@ -1829,22 +1829,22 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>90010</v>
+        <v>90003</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D14" t="s">
         <v>250</v>
       </c>
       <c r="E14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F14" s="1">
-        <v>45812</v>
+        <v>45848</v>
       </c>
       <c r="G14" t="s">
         <v>333</v>
@@ -1853,7 +1853,7 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>14.35</v>
+        <v>58.82</v>
       </c>
       <c r="J14">
         <v>500012</v>
@@ -1864,22 +1864,22 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>90002</v>
+        <v>90001</v>
       </c>
       <c r="B15" t="s">
         <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D15" t="s">
         <v>250</v>
       </c>
       <c r="E15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F15" s="1">
-        <v>45904</v>
+        <v>45718</v>
       </c>
       <c r="G15" t="s">
         <v>333</v>
@@ -1888,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>14.18</v>
+        <v>36.31</v>
       </c>
       <c r="J15">
         <v>500013</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>90005</v>
+        <v>90001</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D16" t="s">
         <v>250</v>
       </c>
       <c r="E16" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F16" s="1">
-        <v>45800</v>
+        <v>45887</v>
       </c>
       <c r="G16" t="s">
         <v>333</v>
@@ -1923,7 +1923,7 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>22.6</v>
+        <v>17.86</v>
       </c>
       <c r="J16">
         <v>500014</v>
@@ -1934,22 +1934,22 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17">
-        <v>90008</v>
+        <v>90005</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D17" t="s">
         <v>250</v>
       </c>
       <c r="E17" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F17" s="1">
-        <v>46017</v>
+        <v>46074</v>
       </c>
       <c r="G17" t="s">
         <v>333</v>
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>40.53</v>
+        <v>37.96</v>
       </c>
       <c r="J17">
         <v>500015</v>
@@ -1969,22 +1969,22 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18">
-        <v>90003</v>
+        <v>90008</v>
       </c>
       <c r="B18" t="s">
         <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D18" t="s">
         <v>250</v>
       </c>
       <c r="E18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F18" s="1">
-        <v>46002</v>
+        <v>45839</v>
       </c>
       <c r="G18" t="s">
         <v>333</v>
@@ -1993,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>30.46</v>
+        <v>13.92</v>
       </c>
       <c r="J18">
         <v>500016</v>
@@ -2004,22 +2004,22 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19">
-        <v>90002</v>
+        <v>90005</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D19" t="s">
         <v>250</v>
       </c>
       <c r="E19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F19" s="1">
-        <v>46053</v>
+        <v>46000</v>
       </c>
       <c r="G19" t="s">
         <v>333</v>
@@ -2028,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>19.81</v>
+        <v>18.34</v>
       </c>
       <c r="J19">
         <v>500017</v>
@@ -2039,22 +2039,22 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20">
-        <v>90006</v>
+        <v>90004</v>
       </c>
       <c r="B20" t="s">
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D20" t="s">
         <v>250</v>
       </c>
       <c r="E20" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F20" s="1">
-        <v>46017</v>
+        <v>46075</v>
       </c>
       <c r="G20" t="s">
         <v>333</v>
@@ -2063,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>46.37</v>
+        <v>10.38</v>
       </c>
       <c r="J20">
         <v>500018</v>
@@ -2074,22 +2074,22 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21">
-        <v>90004</v>
+        <v>90008</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D21" t="s">
         <v>250</v>
       </c>
       <c r="E21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F21" s="1">
-        <v>45945</v>
+        <v>46087</v>
       </c>
       <c r="G21" t="s">
         <v>333</v>
@@ -2098,7 +2098,7 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>14.47</v>
+        <v>28.4</v>
       </c>
       <c r="J21">
         <v>500019</v>
@@ -2109,22 +2109,22 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22">
-        <v>90010</v>
+        <v>90001</v>
       </c>
       <c r="B22" t="s">
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D22" t="s">
         <v>250</v>
       </c>
       <c r="E22" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F22" s="1">
-        <v>45812</v>
+        <v>46100</v>
       </c>
       <c r="G22" t="s">
         <v>333</v>
@@ -2133,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>23.66</v>
+        <v>17.31</v>
       </c>
       <c r="J22">
         <v>500020</v>
@@ -2144,22 +2144,22 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23">
-        <v>90008</v>
+        <v>90004</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D23" t="s">
         <v>250</v>
       </c>
       <c r="E23" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F23" s="1">
-        <v>45734</v>
+        <v>45933</v>
       </c>
       <c r="G23" t="s">
         <v>333</v>
@@ -2168,7 +2168,7 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>19.03</v>
+        <v>25.31</v>
       </c>
       <c r="J23">
         <v>500021</v>
@@ -2179,22 +2179,22 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24">
-        <v>90010</v>
+        <v>90004</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D24" t="s">
         <v>250</v>
       </c>
       <c r="E24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F24" s="1">
-        <v>45826</v>
+        <v>45715</v>
       </c>
       <c r="G24" t="s">
         <v>333</v>
@@ -2203,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>28.44</v>
+        <v>31.83</v>
       </c>
       <c r="J24">
         <v>500022</v>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25">
-        <v>90006</v>
+        <v>90004</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
@@ -2226,10 +2226,10 @@
         <v>250</v>
       </c>
       <c r="E25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F25" s="1">
-        <v>45753</v>
+        <v>45895</v>
       </c>
       <c r="G25" t="s">
         <v>333</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>11.59</v>
+        <v>10.66</v>
       </c>
       <c r="J25">
         <v>500023</v>
@@ -2249,13 +2249,13 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26">
-        <v>90006</v>
+        <v>90005</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D26" t="s">
         <v>250</v>
@@ -2264,7 +2264,7 @@
         <v>256</v>
       </c>
       <c r="F26" s="1">
-        <v>45850</v>
+        <v>45988</v>
       </c>
       <c r="G26" t="s">
         <v>333</v>
@@ -2273,7 +2273,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>26.77</v>
+        <v>19.13</v>
       </c>
       <c r="J26">
         <v>500024</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27">
-        <v>90009</v>
+        <v>90005</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D27" t="s">
         <v>250</v>
       </c>
       <c r="E27" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F27" s="1">
-        <v>46022</v>
+        <v>45853</v>
       </c>
       <c r="G27" t="s">
         <v>333</v>
@@ -2308,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>14.89</v>
+        <v>39.21</v>
       </c>
       <c r="J27">
         <v>500025</v>
@@ -2319,22 +2319,22 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28">
-        <v>90004</v>
+        <v>90006</v>
       </c>
       <c r="B28" t="s">
         <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D28" t="s">
         <v>250</v>
       </c>
       <c r="E28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F28" s="1">
-        <v>45883</v>
+        <v>45864</v>
       </c>
       <c r="G28" t="s">
         <v>333</v>
@@ -2343,7 +2343,7 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>19.9</v>
+        <v>20.22</v>
       </c>
       <c r="J28">
         <v>500026</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29">
-        <v>90005</v>
+        <v>90012</v>
       </c>
       <c r="B29" t="s">
         <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D29" t="s">
         <v>250</v>
       </c>
       <c r="E29" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F29" s="1">
-        <v>45717</v>
+        <v>45761</v>
       </c>
       <c r="G29" t="s">
         <v>333</v>
@@ -2378,7 +2378,7 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>46.93</v>
+        <v>22.04</v>
       </c>
       <c r="J29">
         <v>500027</v>
@@ -2395,16 +2395,16 @@
         <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D30" t="s">
         <v>250</v>
       </c>
       <c r="E30" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F30" s="1">
-        <v>46123</v>
+        <v>45970</v>
       </c>
       <c r="G30" t="s">
         <v>333</v>
@@ -2413,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>16.83</v>
+        <v>56.82</v>
       </c>
       <c r="J30">
         <v>500028</v>
@@ -2424,22 +2424,22 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31">
-        <v>90006</v>
+        <v>90008</v>
       </c>
       <c r="B31" t="s">
         <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D31" t="s">
         <v>250</v>
       </c>
       <c r="E31" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F31" s="1">
-        <v>45733</v>
+        <v>45974</v>
       </c>
       <c r="G31" t="s">
         <v>333</v>
@@ -2448,7 +2448,7 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>44.72</v>
+        <v>34.92</v>
       </c>
       <c r="J31">
         <v>500029</v>
@@ -2459,22 +2459,22 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32">
-        <v>90007</v>
+        <v>90010</v>
       </c>
       <c r="B32" t="s">
         <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D32" t="s">
         <v>250</v>
       </c>
       <c r="E32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F32" s="1">
-        <v>45808</v>
+        <v>45764</v>
       </c>
       <c r="G32" t="s">
         <v>333</v>
@@ -2483,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>48.68</v>
+        <v>10.67</v>
       </c>
       <c r="J32">
         <v>500030</v>
@@ -2494,22 +2494,22 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33">
-        <v>90006</v>
+        <v>90011</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D33" t="s">
         <v>250</v>
       </c>
       <c r="E33" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F33" s="1">
-        <v>45976</v>
+        <v>46074</v>
       </c>
       <c r="G33" t="s">
         <v>333</v>
@@ -2518,7 +2518,7 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>50.06</v>
+        <v>34.9</v>
       </c>
       <c r="J33">
         <v>500031</v>
@@ -2529,22 +2529,22 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34">
-        <v>90002</v>
+        <v>90007</v>
       </c>
       <c r="B34" t="s">
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D34" t="s">
         <v>250</v>
       </c>
       <c r="E34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F34" s="1">
-        <v>45843</v>
+        <v>45784</v>
       </c>
       <c r="G34" t="s">
         <v>333</v>
@@ -2553,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>20.7</v>
+        <v>32.2</v>
       </c>
       <c r="J34">
         <v>500032</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35">
-        <v>90003</v>
+        <v>90006</v>
       </c>
       <c r="B35" t="s">
         <v>45</v>
@@ -2576,10 +2576,10 @@
         <v>250</v>
       </c>
       <c r="E35" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F35" s="1">
-        <v>46077</v>
+        <v>45852</v>
       </c>
       <c r="G35" t="s">
         <v>333</v>
@@ -2588,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>18.14</v>
+        <v>41.42</v>
       </c>
       <c r="J35">
         <v>500033</v>
@@ -2605,16 +2605,16 @@
         <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D36" t="s">
         <v>250</v>
       </c>
       <c r="E36" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F36" s="1">
-        <v>45969</v>
+        <v>45816</v>
       </c>
       <c r="G36" t="s">
         <v>333</v>
@@ -2623,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>24.75</v>
+        <v>29.31</v>
       </c>
       <c r="J36">
         <v>500034</v>
@@ -2634,22 +2634,22 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37">
-        <v>90004</v>
+        <v>90008</v>
       </c>
       <c r="B37" t="s">
         <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D37" t="s">
         <v>250</v>
       </c>
       <c r="E37" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F37" s="1">
-        <v>45959</v>
+        <v>46096</v>
       </c>
       <c r="G37" t="s">
         <v>333</v>
@@ -2658,7 +2658,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>20.15</v>
+        <v>54.67</v>
       </c>
       <c r="J37">
         <v>500035</v>
@@ -2669,22 +2669,22 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38">
-        <v>90001</v>
+        <v>90004</v>
       </c>
       <c r="B38" t="s">
         <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D38" t="s">
         <v>250</v>
       </c>
       <c r="E38" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F38" s="1">
-        <v>46077</v>
+        <v>45873</v>
       </c>
       <c r="G38" t="s">
         <v>333</v>
@@ -2693,7 +2693,7 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>17.26</v>
+        <v>53.34</v>
       </c>
       <c r="J38">
         <v>500036</v>
@@ -2704,22 +2704,22 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39">
-        <v>90010</v>
+        <v>90012</v>
       </c>
       <c r="B39" t="s">
         <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D39" t="s">
         <v>250</v>
       </c>
       <c r="E39" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F39" s="1">
-        <v>45679</v>
+        <v>45916</v>
       </c>
       <c r="G39" t="s">
         <v>333</v>
@@ -2728,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>15.42</v>
+        <v>21.7</v>
       </c>
       <c r="J39">
         <v>500037</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40">
-        <v>90010</v>
+        <v>90009</v>
       </c>
       <c r="B40" t="s">
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D40" t="s">
         <v>250</v>
@@ -2754,7 +2754,7 @@
         <v>257</v>
       </c>
       <c r="F40" s="1">
-        <v>45844</v>
+        <v>45802</v>
       </c>
       <c r="G40" t="s">
         <v>333</v>
@@ -2763,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>19.5</v>
+        <v>53.99</v>
       </c>
       <c r="J40">
         <v>500038</v>
@@ -2774,22 +2774,22 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41">
-        <v>90003</v>
+        <v>90004</v>
       </c>
       <c r="B41" t="s">
         <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D41" t="s">
         <v>250</v>
       </c>
       <c r="E41" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F41" s="1">
-        <v>46105</v>
+        <v>45807</v>
       </c>
       <c r="G41" t="s">
         <v>333</v>
@@ -2798,7 +2798,7 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>39.29</v>
+        <v>17.44</v>
       </c>
       <c r="J41">
         <v>500039</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42">
-        <v>90004</v>
+        <v>90001</v>
       </c>
       <c r="B42" t="s">
         <v>52</v>
       </c>
       <c r="C42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D42" t="s">
         <v>250</v>
       </c>
       <c r="E42" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F42" s="1">
-        <v>45948</v>
+        <v>46020</v>
       </c>
       <c r="G42" t="s">
         <v>333</v>
@@ -2833,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <v>39.95</v>
+        <v>17.84</v>
       </c>
       <c r="J42">
         <v>500040</v>
@@ -2844,13 +2844,13 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43">
-        <v>90012</v>
+        <v>90007</v>
       </c>
       <c r="B43" t="s">
         <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D43" t="s">
         <v>250</v>
@@ -2859,7 +2859,7 @@
         <v>257</v>
       </c>
       <c r="F43" s="1">
-        <v>45891</v>
+        <v>46073</v>
       </c>
       <c r="G43" t="s">
         <v>333</v>
@@ -2868,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>31.75</v>
+        <v>38.08</v>
       </c>
       <c r="J43">
         <v>500041</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44">
-        <v>90004</v>
+        <v>90012</v>
       </c>
       <c r="B44" t="s">
         <v>54</v>
       </c>
       <c r="C44" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D44" t="s">
         <v>250</v>
       </c>
       <c r="E44" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F44" s="1">
-        <v>45898</v>
+        <v>45746</v>
       </c>
       <c r="G44" t="s">
         <v>333</v>
@@ -2903,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>23.55</v>
+        <v>59.87</v>
       </c>
       <c r="J44">
         <v>500042</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45">
-        <v>90004</v>
+        <v>90003</v>
       </c>
       <c r="B45" t="s">
         <v>55</v>
@@ -2926,10 +2926,10 @@
         <v>250</v>
       </c>
       <c r="E45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F45" s="1">
-        <v>46092</v>
+        <v>46041</v>
       </c>
       <c r="G45" t="s">
         <v>333</v>
@@ -2938,7 +2938,7 @@
         <v>1</v>
       </c>
       <c r="I45">
-        <v>17.1</v>
+        <v>52.24</v>
       </c>
       <c r="J45">
         <v>500043</v>
@@ -2949,13 +2949,13 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46">
-        <v>90001</v>
+        <v>90008</v>
       </c>
       <c r="B46" t="s">
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D46" t="s">
         <v>250</v>
@@ -2964,7 +2964,7 @@
         <v>256</v>
       </c>
       <c r="F46" s="1">
-        <v>46003</v>
+        <v>45669</v>
       </c>
       <c r="G46" t="s">
         <v>333</v>
@@ -2973,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>10.78</v>
+        <v>54.3</v>
       </c>
       <c r="J46">
         <v>500044</v>
@@ -2984,13 +2984,13 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47">
-        <v>90011</v>
+        <v>90007</v>
       </c>
       <c r="B47" t="s">
         <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D47" t="s">
         <v>250</v>
@@ -2999,7 +2999,7 @@
         <v>255</v>
       </c>
       <c r="F47" s="1">
-        <v>45833</v>
+        <v>46120</v>
       </c>
       <c r="G47" t="s">
         <v>333</v>
@@ -3008,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>13.71</v>
+        <v>44.41</v>
       </c>
       <c r="J47">
         <v>500045</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48">
-        <v>90012</v>
+        <v>90007</v>
       </c>
       <c r="B48" t="s">
         <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D48" t="s">
         <v>250</v>
       </c>
       <c r="E48" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F48" s="1">
-        <v>46051</v>
+        <v>45774</v>
       </c>
       <c r="G48" t="s">
         <v>333</v>
@@ -3043,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>36.63</v>
+        <v>41.43</v>
       </c>
       <c r="J48">
         <v>500046</v>
@@ -3054,22 +3054,22 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49">
-        <v>90005</v>
+        <v>90002</v>
       </c>
       <c r="B49" t="s">
         <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D49" t="s">
         <v>250</v>
       </c>
       <c r="E49" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F49" s="1">
-        <v>45885</v>
+        <v>45837</v>
       </c>
       <c r="G49" t="s">
         <v>333</v>
@@ -3078,7 +3078,7 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>29.83</v>
+        <v>49.96</v>
       </c>
       <c r="J49">
         <v>500047</v>
@@ -3089,22 +3089,22 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50">
-        <v>90011</v>
+        <v>90012</v>
       </c>
       <c r="B50" t="s">
         <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D50" t="s">
         <v>250</v>
       </c>
       <c r="E50" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F50" s="1">
-        <v>45811</v>
+        <v>46008</v>
       </c>
       <c r="G50" t="s">
         <v>333</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>48.39</v>
+        <v>35.05</v>
       </c>
       <c r="J50">
         <v>500048</v>
@@ -3124,13 +3124,13 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51">
-        <v>90007</v>
+        <v>90008</v>
       </c>
       <c r="B51" t="s">
         <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D51" t="s">
         <v>250</v>
@@ -3139,7 +3139,7 @@
         <v>255</v>
       </c>
       <c r="F51" s="1">
-        <v>45801</v>
+        <v>45978</v>
       </c>
       <c r="G51" t="s">
         <v>333</v>
@@ -3148,7 +3148,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>46.1</v>
+        <v>45.95</v>
       </c>
       <c r="J51">
         <v>500049</v>
@@ -3159,22 +3159,22 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52">
-        <v>90011</v>
+        <v>90003</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D52" t="s">
         <v>250</v>
       </c>
       <c r="E52" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F52" s="1">
-        <v>46011</v>
+        <v>45897</v>
       </c>
       <c r="G52" t="s">
         <v>333</v>
@@ -3183,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>22.32</v>
+        <v>58.54</v>
       </c>
       <c r="J52">
         <v>500050</v>
@@ -3194,19 +3194,19 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53">
-        <v>90008</v>
+        <v>90012</v>
       </c>
       <c r="B53" t="s">
         <v>63</v>
       </c>
       <c r="C53" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D53" t="s">
         <v>250</v>
       </c>
       <c r="E53" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F53" s="1">
         <v>46126</v>
@@ -3218,7 +3218,7 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>16.7</v>
+        <v>20.62</v>
       </c>
       <c r="J53">
         <v>500051</v>
@@ -3229,13 +3229,13 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54">
-        <v>90004</v>
+        <v>90005</v>
       </c>
       <c r="B54" t="s">
         <v>64</v>
       </c>
       <c r="C54" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D54" t="s">
         <v>250</v>
@@ -3244,7 +3244,7 @@
         <v>255</v>
       </c>
       <c r="F54" s="1">
-        <v>45731</v>
+        <v>45855</v>
       </c>
       <c r="G54" t="s">
         <v>333</v>
@@ -3253,7 +3253,7 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <v>40.1</v>
+        <v>35.27</v>
       </c>
       <c r="J54">
         <v>500052</v>
@@ -3264,22 +3264,22 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55">
-        <v>90007</v>
+        <v>90012</v>
       </c>
       <c r="B55" t="s">
         <v>65</v>
       </c>
       <c r="C55" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D55" t="s">
         <v>250</v>
       </c>
       <c r="E55" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F55" s="1">
-        <v>45772</v>
+        <v>46046</v>
       </c>
       <c r="G55" t="s">
         <v>333</v>
@@ -3288,7 +3288,7 @@
         <v>1</v>
       </c>
       <c r="I55">
-        <v>24.95</v>
+        <v>10.23</v>
       </c>
       <c r="J55">
         <v>500053</v>
@@ -3299,22 +3299,22 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56">
-        <v>90011</v>
+        <v>90007</v>
       </c>
       <c r="B56" t="s">
         <v>66</v>
       </c>
       <c r="C56" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D56" t="s">
         <v>250</v>
       </c>
       <c r="E56" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F56" s="1">
-        <v>45906</v>
+        <v>45771</v>
       </c>
       <c r="G56" t="s">
         <v>333</v>
@@ -3323,7 +3323,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>46.12</v>
+        <v>59.94</v>
       </c>
       <c r="J56">
         <v>500054</v>
@@ -3334,13 +3334,13 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57">
-        <v>90003</v>
+        <v>90010</v>
       </c>
       <c r="B57" t="s">
         <v>67</v>
       </c>
       <c r="C57" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D57" t="s">
         <v>250</v>
@@ -3349,7 +3349,7 @@
         <v>257</v>
       </c>
       <c r="F57" s="1">
-        <v>45706</v>
+        <v>45777</v>
       </c>
       <c r="G57" t="s">
         <v>333</v>
@@ -3358,7 +3358,7 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>20.64</v>
+        <v>30.14</v>
       </c>
       <c r="J57">
         <v>500055</v>
@@ -3375,16 +3375,16 @@
         <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D58" t="s">
         <v>250</v>
       </c>
       <c r="E58" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F58" s="1">
-        <v>45886</v>
+        <v>45993</v>
       </c>
       <c r="G58" t="s">
         <v>333</v>
@@ -3393,7 +3393,7 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>53.09</v>
+        <v>46.34</v>
       </c>
       <c r="J58">
         <v>500056</v>
@@ -3404,22 +3404,22 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59">
-        <v>90001</v>
+        <v>90002</v>
       </c>
       <c r="B59" t="s">
         <v>69</v>
       </c>
       <c r="C59" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D59" t="s">
         <v>250</v>
       </c>
       <c r="E59" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F59" s="1">
-        <v>46116</v>
+        <v>45707</v>
       </c>
       <c r="G59" t="s">
         <v>333</v>
@@ -3428,7 +3428,7 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>44</v>
+        <v>56.04</v>
       </c>
       <c r="J59">
         <v>500057</v>
@@ -3439,22 +3439,22 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60">
-        <v>90006</v>
+        <v>90011</v>
       </c>
       <c r="B60" t="s">
         <v>70</v>
       </c>
       <c r="C60" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D60" t="s">
         <v>250</v>
       </c>
       <c r="E60" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F60" s="1">
-        <v>45773</v>
+        <v>45924</v>
       </c>
       <c r="G60" t="s">
         <v>333</v>
@@ -3463,7 +3463,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>53.87</v>
+        <v>50.85</v>
       </c>
       <c r="J60">
         <v>500058</v>
@@ -3474,22 +3474,22 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61">
-        <v>90002</v>
+        <v>90007</v>
       </c>
       <c r="B61" t="s">
         <v>71</v>
       </c>
       <c r="C61" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="D61" t="s">
         <v>250</v>
       </c>
       <c r="E61" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F61" s="1">
-        <v>45982</v>
+        <v>45905</v>
       </c>
       <c r="G61" t="s">
         <v>333</v>
@@ -3498,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>42.69</v>
+        <v>58.73</v>
       </c>
       <c r="J61">
         <v>500059</v>
@@ -3509,22 +3509,22 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62">
-        <v>90011</v>
+        <v>90006</v>
       </c>
       <c r="B62" t="s">
         <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D62" t="s">
         <v>250</v>
       </c>
       <c r="E62" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F62" s="1">
-        <v>45960</v>
+        <v>46123</v>
       </c>
       <c r="G62" t="s">
         <v>333</v>
@@ -3533,7 +3533,7 @@
         <v>1</v>
       </c>
       <c r="I62">
-        <v>16.11</v>
+        <v>44.25</v>
       </c>
       <c r="J62">
         <v>500060</v>
@@ -3544,22 +3544,22 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63">
-        <v>90007</v>
+        <v>90009</v>
       </c>
       <c r="B63" t="s">
         <v>73</v>
       </c>
       <c r="C63" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D63" t="s">
         <v>250</v>
       </c>
       <c r="E63" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F63" s="1">
-        <v>46020</v>
+        <v>45836</v>
       </c>
       <c r="G63" t="s">
         <v>333</v>
@@ -3568,7 +3568,7 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>45.21</v>
+        <v>20.42</v>
       </c>
       <c r="J63">
         <v>500061</v>
@@ -3579,22 +3579,22 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64">
-        <v>90003</v>
+        <v>90004</v>
       </c>
       <c r="B64" t="s">
         <v>74</v>
       </c>
       <c r="C64" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="D64" t="s">
         <v>250</v>
       </c>
       <c r="E64" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F64" s="1">
-        <v>45669</v>
+        <v>45861</v>
       </c>
       <c r="G64" t="s">
         <v>333</v>
@@ -3603,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>50.76</v>
+        <v>35.29</v>
       </c>
       <c r="J64">
         <v>500062</v>
@@ -3614,22 +3614,22 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65">
-        <v>90010</v>
+        <v>90008</v>
       </c>
       <c r="B65" t="s">
         <v>75</v>
       </c>
       <c r="C65" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D65" t="s">
         <v>250</v>
       </c>
       <c r="E65" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F65" s="1">
-        <v>46108</v>
+        <v>45790</v>
       </c>
       <c r="G65" t="s">
         <v>333</v>
@@ -3638,7 +3638,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>56.52</v>
+        <v>55.69</v>
       </c>
       <c r="J65">
         <v>500063</v>
@@ -3649,22 +3649,22 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66">
-        <v>90003</v>
+        <v>90004</v>
       </c>
       <c r="B66" t="s">
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D66" t="s">
         <v>250</v>
       </c>
       <c r="E66" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F66" s="1">
-        <v>46123</v>
+        <v>45743</v>
       </c>
       <c r="G66" t="s">
         <v>333</v>
@@ -3673,7 +3673,7 @@
         <v>1</v>
       </c>
       <c r="I66">
-        <v>10.1</v>
+        <v>37.64</v>
       </c>
       <c r="J66">
         <v>500064</v>
@@ -3684,22 +3684,22 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67">
-        <v>90003</v>
+        <v>90011</v>
       </c>
       <c r="B67" t="s">
         <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D67" t="s">
         <v>250</v>
       </c>
       <c r="E67" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F67" s="1">
-        <v>45781</v>
+        <v>45801</v>
       </c>
       <c r="G67" t="s">
         <v>333</v>
@@ -3708,7 +3708,7 @@
         <v>1</v>
       </c>
       <c r="I67">
-        <v>26.64</v>
+        <v>49.65</v>
       </c>
       <c r="J67">
         <v>500065</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68">
-        <v>90005</v>
+        <v>90008</v>
       </c>
       <c r="B68" t="s">
         <v>78</v>
       </c>
       <c r="C68" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D68" t="s">
         <v>250</v>
       </c>
       <c r="E68" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F68" s="1">
-        <v>46057</v>
+        <v>45996</v>
       </c>
       <c r="G68" t="s">
         <v>333</v>
@@ -3743,7 +3743,7 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>34</v>
+        <v>43.72</v>
       </c>
       <c r="J68">
         <v>500066</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69">
-        <v>90003</v>
+        <v>90004</v>
       </c>
       <c r="B69" t="s">
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D69" t="s">
         <v>250</v>
       </c>
       <c r="E69" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F69" s="1">
-        <v>45819</v>
+        <v>45799</v>
       </c>
       <c r="G69" t="s">
         <v>333</v>
@@ -3778,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>12.38</v>
+        <v>29.4</v>
       </c>
       <c r="J69">
         <v>500067</v>
@@ -3789,7 +3789,7 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70">
-        <v>90012</v>
+        <v>90005</v>
       </c>
       <c r="B70" t="s">
         <v>80</v>
@@ -3801,10 +3801,10 @@
         <v>250</v>
       </c>
       <c r="E70" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F70" s="1">
-        <v>46079</v>
+        <v>45852</v>
       </c>
       <c r="G70" t="s">
         <v>333</v>
@@ -3813,7 +3813,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>26.99</v>
+        <v>52.88</v>
       </c>
       <c r="J70">
         <v>500068</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71">
-        <v>90009</v>
+        <v>90011</v>
       </c>
       <c r="B71" t="s">
         <v>81</v>
       </c>
       <c r="C71" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D71" t="s">
         <v>250</v>
       </c>
       <c r="E71" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F71" s="1">
-        <v>45752</v>
+        <v>46069</v>
       </c>
       <c r="G71" t="s">
         <v>333</v>
@@ -3848,7 +3848,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>46.28</v>
+        <v>18.59</v>
       </c>
       <c r="J71">
         <v>500069</v>
@@ -3859,13 +3859,13 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72">
-        <v>90010</v>
+        <v>90006</v>
       </c>
       <c r="B72" t="s">
         <v>82</v>
       </c>
       <c r="C72" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D72" t="s">
         <v>250</v>
@@ -3874,7 +3874,7 @@
         <v>254</v>
       </c>
       <c r="F72" s="1">
-        <v>45931</v>
+        <v>46072</v>
       </c>
       <c r="G72" t="s">
         <v>333</v>
@@ -3883,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>21.39</v>
+        <v>58.09</v>
       </c>
       <c r="J72">
         <v>500070</v>
@@ -3894,13 +3894,13 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73">
-        <v>90002</v>
+        <v>90004</v>
       </c>
       <c r="B73" t="s">
         <v>83</v>
       </c>
       <c r="C73" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D73" t="s">
         <v>250</v>
@@ -3909,7 +3909,7 @@
         <v>256</v>
       </c>
       <c r="F73" s="1">
-        <v>45896</v>
+        <v>45985</v>
       </c>
       <c r="G73" t="s">
         <v>333</v>
@@ -3918,7 +3918,7 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <v>33.14</v>
+        <v>26.48</v>
       </c>
       <c r="J73">
         <v>500071</v>
@@ -3935,16 +3935,16 @@
         <v>84</v>
       </c>
       <c r="C74" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D74" t="s">
         <v>250</v>
       </c>
       <c r="E74" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F74" s="1">
-        <v>45749</v>
+        <v>45679</v>
       </c>
       <c r="G74" t="s">
         <v>333</v>
@@ -3953,7 +3953,7 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>25.61</v>
+        <v>30.6</v>
       </c>
       <c r="J74">
         <v>500072</v>
@@ -3964,13 +3964,13 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75">
-        <v>90007</v>
+        <v>90004</v>
       </c>
       <c r="B75" t="s">
         <v>85</v>
       </c>
       <c r="C75" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D75" t="s">
         <v>250</v>
@@ -3979,7 +3979,7 @@
         <v>257</v>
       </c>
       <c r="F75" s="1">
-        <v>46060</v>
+        <v>45929</v>
       </c>
       <c r="G75" t="s">
         <v>333</v>
@@ -3988,7 +3988,7 @@
         <v>1</v>
       </c>
       <c r="I75">
-        <v>50.13</v>
+        <v>31.65</v>
       </c>
       <c r="J75">
         <v>500073</v>
@@ -3999,22 +3999,22 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76">
-        <v>90010</v>
+        <v>90005</v>
       </c>
       <c r="B76" t="s">
         <v>86</v>
       </c>
       <c r="C76" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D76" t="s">
         <v>250</v>
       </c>
       <c r="E76" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F76" s="1">
-        <v>45869</v>
+        <v>45732</v>
       </c>
       <c r="G76" t="s">
         <v>333</v>
@@ -4023,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="I76">
-        <v>19.09</v>
+        <v>30.34</v>
       </c>
       <c r="J76">
         <v>500074</v>
@@ -4034,22 +4034,22 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77">
-        <v>90003</v>
+        <v>90007</v>
       </c>
       <c r="B77" t="s">
         <v>87</v>
       </c>
       <c r="C77" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D77" t="s">
         <v>250</v>
       </c>
       <c r="E77" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F77" s="1">
-        <v>45851</v>
+        <v>46129</v>
       </c>
       <c r="G77" t="s">
         <v>333</v>
@@ -4058,7 +4058,7 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <v>59.38</v>
+        <v>13.83</v>
       </c>
       <c r="J77">
         <v>500075</v>
@@ -4075,16 +4075,16 @@
         <v>88</v>
       </c>
       <c r="C78" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D78" t="s">
         <v>250</v>
       </c>
       <c r="E78" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F78" s="1">
-        <v>45938</v>
+        <v>45758</v>
       </c>
       <c r="G78" t="s">
         <v>333</v>
@@ -4093,7 +4093,7 @@
         <v>1</v>
       </c>
       <c r="I78">
-        <v>47.2</v>
+        <v>21.43</v>
       </c>
       <c r="J78">
         <v>500076</v>
@@ -4104,22 +4104,22 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79">
-        <v>90007</v>
+        <v>90011</v>
       </c>
       <c r="B79" t="s">
         <v>89</v>
       </c>
       <c r="C79" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D79" t="s">
         <v>250</v>
       </c>
       <c r="E79" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F79" s="1">
-        <v>45854</v>
+        <v>45661</v>
       </c>
       <c r="G79" t="s">
         <v>333</v>
@@ -4128,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <v>48.23</v>
+        <v>31.7</v>
       </c>
       <c r="J79">
         <v>500077</v>
@@ -4139,22 +4139,22 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80">
-        <v>90004</v>
+        <v>90006</v>
       </c>
       <c r="B80" t="s">
         <v>90</v>
       </c>
       <c r="C80" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D80" t="s">
         <v>250</v>
       </c>
       <c r="E80" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F80" s="1">
-        <v>45730</v>
+        <v>46100</v>
       </c>
       <c r="G80" t="s">
         <v>333</v>
@@ -4163,7 +4163,7 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>29.32</v>
+        <v>20.64</v>
       </c>
       <c r="J80">
         <v>500078</v>
@@ -4174,22 +4174,22 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81">
-        <v>90011</v>
+        <v>90002</v>
       </c>
       <c r="B81" t="s">
         <v>91</v>
       </c>
       <c r="C81" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D81" t="s">
         <v>250</v>
       </c>
       <c r="E81" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F81" s="1">
-        <v>45809</v>
+        <v>45700</v>
       </c>
       <c r="G81" t="s">
         <v>333</v>
@@ -4198,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <v>41.21</v>
+        <v>15.9</v>
       </c>
       <c r="J81">
         <v>500079</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82">
-        <v>90012</v>
+        <v>90009</v>
       </c>
       <c r="B82" t="s">
         <v>92</v>
       </c>
       <c r="C82" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D82" t="s">
         <v>250</v>
       </c>
       <c r="E82" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F82" s="1">
-        <v>45715</v>
+        <v>46084</v>
       </c>
       <c r="G82" t="s">
         <v>333</v>
@@ -4233,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>56.59</v>
+        <v>14.69</v>
       </c>
       <c r="J82">
         <v>500080</v>
@@ -4244,22 +4244,22 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83">
-        <v>90010</v>
+        <v>90008</v>
       </c>
       <c r="B83" t="s">
         <v>93</v>
       </c>
       <c r="C83" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D83" t="s">
         <v>250</v>
       </c>
       <c r="E83" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F83" s="1">
-        <v>45907</v>
+        <v>45936</v>
       </c>
       <c r="G83" t="s">
         <v>333</v>
@@ -4268,7 +4268,7 @@
         <v>1</v>
       </c>
       <c r="I83">
-        <v>36.84</v>
+        <v>17.23</v>
       </c>
       <c r="J83">
         <v>500081</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84">
-        <v>90006</v>
+        <v>90002</v>
       </c>
       <c r="B84" t="s">
         <v>94</v>
       </c>
       <c r="C84" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D84" t="s">
         <v>250</v>
       </c>
       <c r="E84" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F84" s="1">
-        <v>45674</v>
+        <v>46085</v>
       </c>
       <c r="G84" t="s">
         <v>333</v>
@@ -4303,7 +4303,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <v>56.34</v>
+        <v>36.35</v>
       </c>
       <c r="J84">
         <v>500082</v>
@@ -4314,22 +4314,22 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85">
-        <v>90008</v>
+        <v>90005</v>
       </c>
       <c r="B85" t="s">
         <v>95</v>
       </c>
       <c r="C85" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D85" t="s">
         <v>250</v>
       </c>
       <c r="E85" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F85" s="1">
-        <v>46100</v>
+        <v>45762</v>
       </c>
       <c r="G85" t="s">
         <v>333</v>
@@ -4338,7 +4338,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>14.73</v>
+        <v>12.69</v>
       </c>
       <c r="J85">
         <v>500083</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86">
-        <v>90003</v>
+        <v>90006</v>
       </c>
       <c r="B86" t="s">
         <v>96</v>
       </c>
       <c r="C86" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D86" t="s">
         <v>250</v>
       </c>
       <c r="E86" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F86" s="1">
-        <v>45809</v>
+        <v>45905</v>
       </c>
       <c r="G86" t="s">
         <v>333</v>
@@ -4373,7 +4373,7 @@
         <v>1</v>
       </c>
       <c r="I86">
-        <v>21.35</v>
+        <v>33.9</v>
       </c>
       <c r="J86">
         <v>500084</v>
@@ -4384,22 +4384,22 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87">
-        <v>90003</v>
+        <v>90012</v>
       </c>
       <c r="B87" t="s">
         <v>97</v>
       </c>
       <c r="C87" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D87" t="s">
         <v>250</v>
       </c>
       <c r="E87" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F87" s="1">
-        <v>45783</v>
+        <v>45846</v>
       </c>
       <c r="G87" t="s">
         <v>333</v>
@@ -4408,7 +4408,7 @@
         <v>1</v>
       </c>
       <c r="I87">
-        <v>38.5</v>
+        <v>16.01</v>
       </c>
       <c r="J87">
         <v>500085</v>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88">
-        <v>90011</v>
+        <v>90005</v>
       </c>
       <c r="B88" t="s">
         <v>98</v>
       </c>
       <c r="C88" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D88" t="s">
         <v>250</v>
       </c>
       <c r="E88" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F88" s="1">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="G88" t="s">
         <v>333</v>
@@ -4443,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="I88">
-        <v>52.01</v>
+        <v>20.51</v>
       </c>
       <c r="J88">
         <v>500086</v>
@@ -4454,22 +4454,22 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89">
-        <v>90005</v>
+        <v>90002</v>
       </c>
       <c r="B89" t="s">
         <v>99</v>
       </c>
       <c r="C89" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D89" t="s">
         <v>250</v>
       </c>
       <c r="E89" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F89" s="1">
-        <v>45951</v>
+        <v>46006</v>
       </c>
       <c r="G89" t="s">
         <v>333</v>
@@ -4478,7 +4478,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <v>38.85</v>
+        <v>57.85</v>
       </c>
       <c r="J89">
         <v>500087</v>
@@ -4489,13 +4489,13 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90">
-        <v>90008</v>
+        <v>90004</v>
       </c>
       <c r="B90" t="s">
         <v>100</v>
       </c>
       <c r="C90" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D90" t="s">
         <v>250</v>
@@ -4504,7 +4504,7 @@
         <v>254</v>
       </c>
       <c r="F90" s="1">
-        <v>46047</v>
+        <v>45682</v>
       </c>
       <c r="G90" t="s">
         <v>333</v>
@@ -4513,7 +4513,7 @@
         <v>1</v>
       </c>
       <c r="I90">
-        <v>44.52</v>
+        <v>23.01</v>
       </c>
       <c r="J90">
         <v>500088</v>
@@ -4530,7 +4530,7 @@
         <v>101</v>
       </c>
       <c r="C91" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D91" t="s">
         <v>250</v>
@@ -4539,7 +4539,7 @@
         <v>257</v>
       </c>
       <c r="F91" s="1">
-        <v>45961</v>
+        <v>45694</v>
       </c>
       <c r="G91" t="s">
         <v>333</v>
@@ -4548,7 +4548,7 @@
         <v>1</v>
       </c>
       <c r="I91">
-        <v>54.67</v>
+        <v>21.78</v>
       </c>
       <c r="J91">
         <v>500089</v>
@@ -4559,22 +4559,22 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92">
-        <v>90001</v>
+        <v>90012</v>
       </c>
       <c r="B92" t="s">
         <v>102</v>
       </c>
       <c r="C92" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D92" t="s">
         <v>250</v>
       </c>
       <c r="E92" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F92" s="1">
-        <v>46054</v>
+        <v>45869</v>
       </c>
       <c r="G92" t="s">
         <v>333</v>
@@ -4583,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="I92">
-        <v>55.89</v>
+        <v>31.13</v>
       </c>
       <c r="J92">
         <v>500090</v>
@@ -4594,22 +4594,22 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93">
-        <v>90012</v>
+        <v>90006</v>
       </c>
       <c r="B93" t="s">
         <v>103</v>
       </c>
       <c r="C93" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D93" t="s">
         <v>250</v>
       </c>
       <c r="E93" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F93" s="1">
-        <v>46106</v>
+        <v>45922</v>
       </c>
       <c r="G93" t="s">
         <v>333</v>
@@ -4618,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>52.25</v>
+        <v>51.67</v>
       </c>
       <c r="J93">
         <v>500091</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94">
-        <v>90008</v>
+        <v>90001</v>
       </c>
       <c r="B94" t="s">
         <v>104</v>
       </c>
       <c r="C94" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D94" t="s">
         <v>250</v>
       </c>
       <c r="E94" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F94" s="1">
-        <v>46057</v>
+        <v>45875</v>
       </c>
       <c r="G94" t="s">
         <v>333</v>
@@ -4653,7 +4653,7 @@
         <v>1</v>
       </c>
       <c r="I94">
-        <v>52.41</v>
+        <v>36.72</v>
       </c>
       <c r="J94">
         <v>500092</v>
@@ -4664,22 +4664,22 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95">
-        <v>90007</v>
+        <v>90006</v>
       </c>
       <c r="B95" t="s">
         <v>105</v>
       </c>
       <c r="C95" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D95" t="s">
         <v>250</v>
       </c>
       <c r="E95" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F95" s="1">
-        <v>46112</v>
+        <v>45806</v>
       </c>
       <c r="G95" t="s">
         <v>333</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="I95">
-        <v>23.12</v>
+        <v>26.82</v>
       </c>
       <c r="J95">
         <v>500093</v>
@@ -4699,22 +4699,22 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96">
-        <v>90008</v>
+        <v>90011</v>
       </c>
       <c r="B96" t="s">
         <v>106</v>
       </c>
       <c r="C96" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D96" t="s">
         <v>250</v>
       </c>
       <c r="E96" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F96" s="1">
-        <v>46116</v>
+        <v>46086</v>
       </c>
       <c r="G96" t="s">
         <v>333</v>
@@ -4723,7 +4723,7 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <v>23.16</v>
+        <v>54.16</v>
       </c>
       <c r="J96">
         <v>500094</v>
@@ -4734,22 +4734,22 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97">
-        <v>90002</v>
+        <v>90005</v>
       </c>
       <c r="B97" t="s">
         <v>107</v>
       </c>
       <c r="C97" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D97" t="s">
         <v>250</v>
       </c>
       <c r="E97" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F97" s="1">
-        <v>45931</v>
+        <v>46037</v>
       </c>
       <c r="G97" t="s">
         <v>333</v>
@@ -4758,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>44.14</v>
+        <v>49.45</v>
       </c>
       <c r="J97">
         <v>500095</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98">
-        <v>90011</v>
+        <v>90007</v>
       </c>
       <c r="B98" t="s">
         <v>108</v>
@@ -4781,10 +4781,10 @@
         <v>250</v>
       </c>
       <c r="E98" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F98" s="1">
-        <v>46137</v>
+        <v>45905</v>
       </c>
       <c r="G98" t="s">
         <v>333</v>
@@ -4793,7 +4793,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>40.72</v>
+        <v>41.93</v>
       </c>
       <c r="J98">
         <v>500096</v>
@@ -4804,22 +4804,22 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99">
-        <v>90012</v>
+        <v>90008</v>
       </c>
       <c r="B99" t="s">
         <v>109</v>
       </c>
       <c r="C99" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D99" t="s">
         <v>250</v>
       </c>
       <c r="E99" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F99" s="1">
-        <v>45906</v>
+        <v>46021</v>
       </c>
       <c r="G99" t="s">
         <v>333</v>
@@ -4828,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="I99">
-        <v>13.07</v>
+        <v>15.84</v>
       </c>
       <c r="J99">
         <v>500097</v>
@@ -4839,7 +4839,7 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100">
-        <v>90009</v>
+        <v>90010</v>
       </c>
       <c r="B100" t="s">
         <v>110</v>
@@ -4851,10 +4851,10 @@
         <v>250</v>
       </c>
       <c r="E100" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F100" s="1">
-        <v>45908</v>
+        <v>45804</v>
       </c>
       <c r="G100" t="s">
         <v>333</v>
@@ -4863,7 +4863,7 @@
         <v>1</v>
       </c>
       <c r="I100">
-        <v>23.05</v>
+        <v>26.66</v>
       </c>
       <c r="J100">
         <v>500098</v>
@@ -4874,7 +4874,7 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101">
-        <v>90009</v>
+        <v>90008</v>
       </c>
       <c r="B101" t="s">
         <v>111</v>
@@ -4886,10 +4886,10 @@
         <v>250</v>
       </c>
       <c r="E101" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F101" s="1">
-        <v>45880</v>
+        <v>45947</v>
       </c>
       <c r="G101" t="s">
         <v>333</v>
@@ -4898,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="I101">
-        <v>49.39</v>
+        <v>33.23</v>
       </c>
       <c r="J101">
         <v>500099</v>
@@ -4909,22 +4909,22 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102">
-        <v>90002</v>
+        <v>90012</v>
       </c>
       <c r="B102" t="s">
         <v>112</v>
       </c>
       <c r="C102" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D102" t="s">
         <v>250</v>
       </c>
       <c r="E102" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F102" s="1">
-        <v>45658</v>
+        <v>45810</v>
       </c>
       <c r="G102" t="s">
         <v>333</v>
@@ -4933,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>28.67</v>
+        <v>44.97</v>
       </c>
       <c r="J102">
         <v>500100</v>
@@ -4944,22 +4944,22 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103">
-        <v>90010</v>
+        <v>90011</v>
       </c>
       <c r="B103" t="s">
         <v>113</v>
       </c>
       <c r="C103" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D103" t="s">
         <v>250</v>
       </c>
       <c r="E103" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F103" s="1">
-        <v>45874</v>
+        <v>46036</v>
       </c>
       <c r="G103" t="s">
         <v>333</v>
@@ -4968,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="I103">
-        <v>26.84</v>
+        <v>21.62</v>
       </c>
       <c r="J103">
         <v>500101</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104">
-        <v>90001</v>
+        <v>90010</v>
       </c>
       <c r="B104" t="s">
         <v>114</v>
@@ -4991,10 +4991,10 @@
         <v>250</v>
       </c>
       <c r="E104" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F104" s="1">
-        <v>45843</v>
+        <v>45930</v>
       </c>
       <c r="G104" t="s">
         <v>333</v>
@@ -5003,7 +5003,7 @@
         <v>1</v>
       </c>
       <c r="I104">
-        <v>42.36</v>
+        <v>26.4</v>
       </c>
       <c r="J104">
         <v>500102</v>
@@ -5014,22 +5014,22 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105">
-        <v>90004</v>
+        <v>90006</v>
       </c>
       <c r="B105" t="s">
         <v>115</v>
       </c>
       <c r="C105" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D105" t="s">
         <v>250</v>
       </c>
       <c r="E105" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F105" s="1">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="G105" t="s">
         <v>333</v>
@@ -5038,7 +5038,7 @@
         <v>1</v>
       </c>
       <c r="I105">
-        <v>21.12</v>
+        <v>45.96</v>
       </c>
       <c r="J105">
         <v>500103</v>
@@ -5049,7 +5049,7 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106">
-        <v>90004</v>
+        <v>90008</v>
       </c>
       <c r="B106" t="s">
         <v>116</v>
@@ -5064,7 +5064,7 @@
         <v>254</v>
       </c>
       <c r="F106" s="1">
-        <v>46039</v>
+        <v>45966</v>
       </c>
       <c r="G106" t="s">
         <v>333</v>
@@ -5073,7 +5073,7 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>59.13</v>
+        <v>12.48</v>
       </c>
       <c r="J106">
         <v>500104</v>
@@ -5084,22 +5084,22 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107">
-        <v>90004</v>
+        <v>90005</v>
       </c>
       <c r="B107" t="s">
         <v>117</v>
       </c>
       <c r="C107" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D107" t="s">
         <v>250</v>
       </c>
       <c r="E107" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F107" s="1">
-        <v>46088</v>
+        <v>45831</v>
       </c>
       <c r="G107" t="s">
         <v>333</v>
@@ -5108,7 +5108,7 @@
         <v>1</v>
       </c>
       <c r="I107">
-        <v>27.34</v>
+        <v>17.59</v>
       </c>
       <c r="J107">
         <v>500105</v>
@@ -5119,22 +5119,22 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108">
-        <v>90004</v>
+        <v>90010</v>
       </c>
       <c r="B108" t="s">
         <v>118</v>
       </c>
       <c r="C108" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D108" t="s">
         <v>250</v>
       </c>
       <c r="E108" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F108" s="1">
-        <v>45790</v>
+        <v>45889</v>
       </c>
       <c r="G108" t="s">
         <v>333</v>
@@ -5143,7 +5143,7 @@
         <v>1</v>
       </c>
       <c r="I108">
-        <v>52.01</v>
+        <v>12.15</v>
       </c>
       <c r="J108">
         <v>500106</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109">
-        <v>90008</v>
+        <v>90010</v>
       </c>
       <c r="B109" t="s">
         <v>119</v>
       </c>
       <c r="C109" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D109" t="s">
         <v>250</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F109" s="1">
-        <v>45954</v>
+        <v>45781</v>
       </c>
       <c r="G109" t="s">
         <v>333</v>
@@ -5178,7 +5178,7 @@
         <v>1</v>
       </c>
       <c r="I109">
-        <v>19.87</v>
+        <v>23.99</v>
       </c>
       <c r="J109">
         <v>500107</v>
@@ -5189,22 +5189,22 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110">
-        <v>90004</v>
+        <v>90011</v>
       </c>
       <c r="B110" t="s">
         <v>120</v>
       </c>
       <c r="C110" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D110" t="s">
         <v>250</v>
       </c>
       <c r="E110" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F110" s="1">
-        <v>45994</v>
+        <v>46058</v>
       </c>
       <c r="G110" t="s">
         <v>333</v>
@@ -5213,7 +5213,7 @@
         <v>1</v>
       </c>
       <c r="I110">
-        <v>45.49</v>
+        <v>32.94</v>
       </c>
       <c r="J110">
         <v>500108</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111">
-        <v>90006</v>
+        <v>90010</v>
       </c>
       <c r="B111" t="s">
         <v>121</v>
       </c>
       <c r="C111" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D111" t="s">
         <v>250</v>
       </c>
       <c r="E111" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F111" s="1">
-        <v>45984</v>
+        <v>45763</v>
       </c>
       <c r="G111" t="s">
         <v>333</v>
@@ -5248,7 +5248,7 @@
         <v>1</v>
       </c>
       <c r="I111">
-        <v>53.96</v>
+        <v>51.81</v>
       </c>
       <c r="J111">
         <v>500109</v>
@@ -5259,22 +5259,22 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112">
-        <v>90007</v>
+        <v>90010</v>
       </c>
       <c r="B112" t="s">
         <v>122</v>
       </c>
       <c r="C112" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D112" t="s">
         <v>250</v>
       </c>
       <c r="E112" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F112" s="1">
-        <v>45948</v>
+        <v>45690</v>
       </c>
       <c r="G112" t="s">
         <v>333</v>
@@ -5283,7 +5283,7 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>18.97</v>
+        <v>27.28</v>
       </c>
       <c r="J112">
         <v>500110</v>
@@ -5294,22 +5294,22 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113">
-        <v>90007</v>
+        <v>90006</v>
       </c>
       <c r="B113" t="s">
         <v>123</v>
       </c>
       <c r="C113" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D113" t="s">
         <v>250</v>
       </c>
       <c r="E113" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F113" s="1">
-        <v>45689</v>
+        <v>45783</v>
       </c>
       <c r="G113" t="s">
         <v>333</v>
@@ -5318,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>19.1</v>
+        <v>43.22</v>
       </c>
       <c r="J113">
         <v>500111</v>
@@ -5329,13 +5329,13 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114">
-        <v>90012</v>
+        <v>90008</v>
       </c>
       <c r="B114" t="s">
         <v>124</v>
       </c>
       <c r="C114" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D114" t="s">
         <v>250</v>
@@ -5344,7 +5344,7 @@
         <v>255</v>
       </c>
       <c r="F114" s="1">
-        <v>45658</v>
+        <v>45916</v>
       </c>
       <c r="G114" t="s">
         <v>333</v>
@@ -5353,7 +5353,7 @@
         <v>1</v>
       </c>
       <c r="I114">
-        <v>59.2</v>
+        <v>52.71</v>
       </c>
       <c r="J114">
         <v>500112</v>
@@ -5364,22 +5364,22 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115">
-        <v>90004</v>
+        <v>90001</v>
       </c>
       <c r="B115" t="s">
         <v>125</v>
       </c>
       <c r="C115" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D115" t="s">
         <v>250</v>
       </c>
       <c r="E115" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F115" s="1">
-        <v>46049</v>
+        <v>46038</v>
       </c>
       <c r="G115" t="s">
         <v>333</v>
@@ -5388,7 +5388,7 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>11.71</v>
+        <v>31.08</v>
       </c>
       <c r="J115">
         <v>500113</v>
@@ -5399,22 +5399,22 @@
     </row>
     <row r="116" spans="1:12">
       <c r="A116">
-        <v>90003</v>
+        <v>90012</v>
       </c>
       <c r="B116" t="s">
         <v>126</v>
       </c>
       <c r="C116" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D116" t="s">
         <v>250</v>
       </c>
       <c r="E116" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F116" s="1">
-        <v>45733</v>
+        <v>45954</v>
       </c>
       <c r="G116" t="s">
         <v>333</v>
@@ -5423,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="I116">
-        <v>31.61</v>
+        <v>12.24</v>
       </c>
       <c r="J116">
         <v>500114</v>
@@ -5434,22 +5434,22 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117">
-        <v>90008</v>
+        <v>90001</v>
       </c>
       <c r="B117" t="s">
         <v>127</v>
       </c>
       <c r="C117" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D117" t="s">
         <v>250</v>
       </c>
       <c r="E117" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F117" s="1">
-        <v>46082</v>
+        <v>45726</v>
       </c>
       <c r="G117" t="s">
         <v>333</v>
@@ -5458,7 +5458,7 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>54.86</v>
+        <v>53.93</v>
       </c>
       <c r="J117">
         <v>500115</v>
@@ -5469,13 +5469,13 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118">
-        <v>90004</v>
+        <v>90011</v>
       </c>
       <c r="B118" t="s">
         <v>128</v>
       </c>
       <c r="C118" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D118" t="s">
         <v>250</v>
@@ -5484,7 +5484,7 @@
         <v>256</v>
       </c>
       <c r="F118" s="1">
-        <v>46049</v>
+        <v>45660</v>
       </c>
       <c r="G118" t="s">
         <v>333</v>
@@ -5493,7 +5493,7 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>51.45</v>
+        <v>45.04</v>
       </c>
       <c r="J118">
         <v>500116</v>
@@ -5504,22 +5504,22 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119">
-        <v>90011</v>
+        <v>90004</v>
       </c>
       <c r="B119" t="s">
         <v>129</v>
       </c>
       <c r="C119" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D119" t="s">
         <v>250</v>
       </c>
       <c r="E119" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F119" s="1">
-        <v>46023</v>
+        <v>45903</v>
       </c>
       <c r="G119" t="s">
         <v>333</v>
@@ -5528,7 +5528,7 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>46.71</v>
+        <v>31.33</v>
       </c>
       <c r="J119">
         <v>500117</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120">
-        <v>90004</v>
+        <v>90009</v>
       </c>
       <c r="B120" t="s">
         <v>130</v>
@@ -5551,10 +5551,10 @@
         <v>250</v>
       </c>
       <c r="E120" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F120" s="1">
-        <v>45851</v>
+        <v>46083</v>
       </c>
       <c r="G120" t="s">
         <v>333</v>
@@ -5563,7 +5563,7 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>40.72</v>
+        <v>45.11</v>
       </c>
       <c r="J120">
         <v>500118</v>
@@ -5580,16 +5580,16 @@
         <v>131</v>
       </c>
       <c r="C121" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D121" t="s">
         <v>250</v>
       </c>
       <c r="E121" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F121" s="1">
-        <v>45784</v>
+        <v>45780</v>
       </c>
       <c r="G121" t="s">
         <v>333</v>
@@ -5598,7 +5598,7 @@
         <v>1</v>
       </c>
       <c r="I121">
-        <v>58.44</v>
+        <v>29.65</v>
       </c>
       <c r="J121">
         <v>500119</v>
@@ -5609,22 +5609,22 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122">
-        <v>90004</v>
+        <v>90009</v>
       </c>
       <c r="B122" t="s">
         <v>132</v>
       </c>
       <c r="C122" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D122" t="s">
         <v>250</v>
       </c>
       <c r="E122" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F122" s="1">
-        <v>45751</v>
+        <v>45691</v>
       </c>
       <c r="G122" t="s">
         <v>333</v>
@@ -5633,7 +5633,7 @@
         <v>1</v>
       </c>
       <c r="I122">
-        <v>48.29</v>
+        <v>16.85</v>
       </c>
       <c r="J122">
         <v>500120</v>
@@ -5644,22 +5644,22 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123">
-        <v>90007</v>
+        <v>90011</v>
       </c>
       <c r="B123" t="s">
         <v>133</v>
       </c>
       <c r="C123" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D123" t="s">
         <v>250</v>
       </c>
       <c r="E123" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F123" s="1">
-        <v>45912</v>
+        <v>45947</v>
       </c>
       <c r="G123" t="s">
         <v>333</v>
@@ -5668,7 +5668,7 @@
         <v>1</v>
       </c>
       <c r="I123">
-        <v>20.27</v>
+        <v>42.06</v>
       </c>
       <c r="J123">
         <v>500121</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124">
-        <v>90004</v>
+        <v>90009</v>
       </c>
       <c r="B124" t="s">
         <v>134</v>
       </c>
       <c r="C124" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D124" t="s">
         <v>250</v>
       </c>
       <c r="E124" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F124" s="1">
-        <v>46006</v>
+        <v>46141</v>
       </c>
       <c r="G124" t="s">
         <v>333</v>
@@ -5703,7 +5703,7 @@
         <v>1</v>
       </c>
       <c r="I124">
-        <v>30.33</v>
+        <v>38.19</v>
       </c>
       <c r="J124">
         <v>500122</v>
@@ -5714,22 +5714,22 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125">
-        <v>90005</v>
+        <v>90009</v>
       </c>
       <c r="B125" t="s">
         <v>135</v>
       </c>
       <c r="C125" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D125" t="s">
         <v>250</v>
       </c>
       <c r="E125" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F125" s="1">
-        <v>45915</v>
+        <v>46093</v>
       </c>
       <c r="G125" t="s">
         <v>333</v>
@@ -5738,7 +5738,7 @@
         <v>1</v>
       </c>
       <c r="I125">
-        <v>32.44</v>
+        <v>16.65</v>
       </c>
       <c r="J125">
         <v>500123</v>
@@ -5749,7 +5749,7 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126">
-        <v>90003</v>
+        <v>90007</v>
       </c>
       <c r="B126" t="s">
         <v>136</v>
@@ -5764,7 +5764,7 @@
         <v>258</v>
       </c>
       <c r="F126" s="1">
-        <v>45738</v>
+        <v>45823</v>
       </c>
       <c r="G126" t="s">
         <v>333</v>
@@ -5773,7 +5773,7 @@
         <v>1</v>
       </c>
       <c r="I126">
-        <v>24.89</v>
+        <v>40.3</v>
       </c>
       <c r="J126">
         <v>500124</v>
@@ -5784,22 +5784,22 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127">
-        <v>90006</v>
+        <v>90005</v>
       </c>
       <c r="B127" t="s">
         <v>137</v>
       </c>
       <c r="C127" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D127" t="s">
         <v>250</v>
       </c>
       <c r="E127" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F127" s="1">
-        <v>45724</v>
+        <v>46060</v>
       </c>
       <c r="G127" t="s">
         <v>333</v>
@@ -5808,7 +5808,7 @@
         <v>1</v>
       </c>
       <c r="I127">
-        <v>37.91</v>
+        <v>34.13</v>
       </c>
       <c r="J127">
         <v>500125</v>
@@ -5825,16 +5825,16 @@
         <v>138</v>
       </c>
       <c r="C128" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D128" t="s">
         <v>250</v>
       </c>
       <c r="E128" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F128" s="1">
-        <v>46016</v>
+        <v>46102</v>
       </c>
       <c r="G128" t="s">
         <v>333</v>
@@ -5843,7 +5843,7 @@
         <v>1</v>
       </c>
       <c r="I128">
-        <v>50.52</v>
+        <v>29.81</v>
       </c>
       <c r="J128">
         <v>500126</v>
@@ -5854,22 +5854,22 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129">
-        <v>90009</v>
+        <v>90004</v>
       </c>
       <c r="B129" t="s">
         <v>139</v>
       </c>
       <c r="C129" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D129" t="s">
         <v>250</v>
       </c>
       <c r="E129" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F129" s="1">
-        <v>45780</v>
+        <v>45833</v>
       </c>
       <c r="G129" t="s">
         <v>333</v>
@@ -5878,7 +5878,7 @@
         <v>1</v>
       </c>
       <c r="I129">
-        <v>24.58</v>
+        <v>29.56</v>
       </c>
       <c r="J129">
         <v>500127</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130">
-        <v>90004</v>
+        <v>90005</v>
       </c>
       <c r="B130" t="s">
         <v>140</v>
       </c>
       <c r="C130" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D130" t="s">
         <v>250</v>
       </c>
       <c r="E130" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F130" s="1">
-        <v>46141</v>
+        <v>45713</v>
       </c>
       <c r="G130" t="s">
         <v>333</v>
@@ -5913,7 +5913,7 @@
         <v>1</v>
       </c>
       <c r="I130">
-        <v>55.36</v>
+        <v>49.39</v>
       </c>
       <c r="J130">
         <v>500128</v>
@@ -5924,22 +5924,22 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131">
-        <v>90004</v>
+        <v>90011</v>
       </c>
       <c r="B131" t="s">
         <v>141</v>
       </c>
       <c r="C131" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D131" t="s">
         <v>250</v>
       </c>
       <c r="E131" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F131" s="1">
-        <v>45699</v>
+        <v>46003</v>
       </c>
       <c r="G131" t="s">
         <v>333</v>
@@ -5948,7 +5948,7 @@
         <v>1</v>
       </c>
       <c r="I131">
-        <v>42.6</v>
+        <v>15.18</v>
       </c>
       <c r="J131">
         <v>500129</v>
@@ -5959,22 +5959,22 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132">
-        <v>90008</v>
+        <v>90004</v>
       </c>
       <c r="B132" t="s">
         <v>142</v>
       </c>
       <c r="C132" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D132" t="s">
         <v>250</v>
       </c>
       <c r="E132" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F132" s="1">
-        <v>46055</v>
+        <v>45720</v>
       </c>
       <c r="G132" t="s">
         <v>333</v>
@@ -5983,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="I132">
-        <v>26.72</v>
+        <v>20.21</v>
       </c>
       <c r="J132">
         <v>500130</v>
@@ -5994,22 +5994,22 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133">
-        <v>90003</v>
+        <v>90008</v>
       </c>
       <c r="B133" t="s">
         <v>143</v>
       </c>
       <c r="C133" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D133" t="s">
         <v>250</v>
       </c>
       <c r="E133" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F133" s="1">
-        <v>45770</v>
+        <v>46098</v>
       </c>
       <c r="G133" t="s">
         <v>333</v>
@@ -6018,7 +6018,7 @@
         <v>1</v>
       </c>
       <c r="I133">
-        <v>51.1</v>
+        <v>49.61</v>
       </c>
       <c r="J133">
         <v>500131</v>
@@ -6029,22 +6029,22 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134">
-        <v>90009</v>
+        <v>90001</v>
       </c>
       <c r="B134" t="s">
         <v>144</v>
       </c>
       <c r="C134" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D134" t="s">
         <v>250</v>
       </c>
       <c r="E134" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F134" s="1">
-        <v>46018</v>
+        <v>45923</v>
       </c>
       <c r="G134" t="s">
         <v>333</v>
@@ -6053,7 +6053,7 @@
         <v>1</v>
       </c>
       <c r="I134">
-        <v>43.85</v>
+        <v>57.74</v>
       </c>
       <c r="J134">
         <v>500132</v>
@@ -6064,7 +6064,7 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135">
-        <v>90008</v>
+        <v>90002</v>
       </c>
       <c r="B135" t="s">
         <v>145</v>
@@ -6079,7 +6079,7 @@
         <v>256</v>
       </c>
       <c r="F135" s="1">
-        <v>46133</v>
+        <v>45984</v>
       </c>
       <c r="G135" t="s">
         <v>333</v>
@@ -6088,7 +6088,7 @@
         <v>1</v>
       </c>
       <c r="I135">
-        <v>39.39</v>
+        <v>32.39</v>
       </c>
       <c r="J135">
         <v>500133</v>
@@ -6099,22 +6099,22 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136">
-        <v>90011</v>
+        <v>90009</v>
       </c>
       <c r="B136" t="s">
         <v>146</v>
       </c>
       <c r="C136" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D136" t="s">
         <v>250</v>
       </c>
       <c r="E136" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F136" s="1">
-        <v>45808</v>
+        <v>46139</v>
       </c>
       <c r="G136" t="s">
         <v>333</v>
@@ -6123,7 +6123,7 @@
         <v>1</v>
       </c>
       <c r="I136">
-        <v>15.58</v>
+        <v>50.43</v>
       </c>
       <c r="J136">
         <v>500134</v>
@@ -6134,22 +6134,22 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137">
-        <v>90010</v>
+        <v>90011</v>
       </c>
       <c r="B137" t="s">
         <v>147</v>
       </c>
       <c r="C137" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D137" t="s">
         <v>250</v>
       </c>
       <c r="E137" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F137" s="1">
-        <v>45950</v>
+        <v>46023</v>
       </c>
       <c r="G137" t="s">
         <v>333</v>
@@ -6158,7 +6158,7 @@
         <v>1</v>
       </c>
       <c r="I137">
-        <v>40.19</v>
+        <v>36.25</v>
       </c>
       <c r="J137">
         <v>500135</v>
@@ -6169,7 +6169,7 @@
     </row>
     <row r="138" spans="1:12">
       <c r="A138">
-        <v>90006</v>
+        <v>90005</v>
       </c>
       <c r="B138" t="s">
         <v>148</v>
@@ -6181,10 +6181,10 @@
         <v>250</v>
       </c>
       <c r="E138" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F138" s="1">
-        <v>45819</v>
+        <v>45962</v>
       </c>
       <c r="G138" t="s">
         <v>333</v>
@@ -6193,7 +6193,7 @@
         <v>1</v>
       </c>
       <c r="I138">
-        <v>45.6</v>
+        <v>47.15</v>
       </c>
       <c r="J138">
         <v>500136</v>
@@ -6204,22 +6204,22 @@
     </row>
     <row r="139" spans="1:12">
       <c r="A139">
-        <v>90001</v>
+        <v>90011</v>
       </c>
       <c r="B139" t="s">
         <v>149</v>
       </c>
       <c r="C139" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D139" t="s">
         <v>250</v>
       </c>
       <c r="E139" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F139" s="1">
-        <v>46043</v>
+        <v>45797</v>
       </c>
       <c r="G139" t="s">
         <v>333</v>
@@ -6228,7 +6228,7 @@
         <v>1</v>
       </c>
       <c r="I139">
-        <v>52.36</v>
+        <v>34.87</v>
       </c>
       <c r="J139">
         <v>500137</v>
@@ -6239,22 +6239,22 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140">
-        <v>90001</v>
+        <v>90012</v>
       </c>
       <c r="B140" t="s">
         <v>150</v>
       </c>
       <c r="C140" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D140" t="s">
         <v>250</v>
       </c>
       <c r="E140" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F140" s="1">
-        <v>45789</v>
+        <v>45732</v>
       </c>
       <c r="G140" t="s">
         <v>333</v>
@@ -6263,7 +6263,7 @@
         <v>1</v>
       </c>
       <c r="I140">
-        <v>31.78</v>
+        <v>34.84</v>
       </c>
       <c r="J140">
         <v>500138</v>
@@ -6274,22 +6274,22 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141">
-        <v>90003</v>
+        <v>90002</v>
       </c>
       <c r="B141" t="s">
         <v>151</v>
       </c>
       <c r="C141" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D141" t="s">
         <v>250</v>
       </c>
       <c r="E141" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F141" s="1">
-        <v>46049</v>
+        <v>45936</v>
       </c>
       <c r="G141" t="s">
         <v>333</v>
@@ -6298,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="I141">
-        <v>24.95</v>
+        <v>46.53</v>
       </c>
       <c r="J141">
         <v>500139</v>
@@ -6309,7 +6309,7 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142">
-        <v>90002</v>
+        <v>90010</v>
       </c>
       <c r="B142" t="s">
         <v>152</v>
@@ -6321,10 +6321,10 @@
         <v>250</v>
       </c>
       <c r="E142" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F142" s="1">
-        <v>45760</v>
+        <v>45761</v>
       </c>
       <c r="G142" t="s">
         <v>333</v>
@@ -6333,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="I142">
-        <v>31.65</v>
+        <v>36.62</v>
       </c>
       <c r="J142">
         <v>500140</v>
@@ -6344,22 +6344,22 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143">
-        <v>90005</v>
+        <v>90010</v>
       </c>
       <c r="B143" t="s">
         <v>153</v>
       </c>
       <c r="C143" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D143" t="s">
         <v>250</v>
       </c>
       <c r="E143" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F143" s="1">
-        <v>45881</v>
+        <v>45888</v>
       </c>
       <c r="G143" t="s">
         <v>333</v>
@@ -6368,7 +6368,7 @@
         <v>1</v>
       </c>
       <c r="I143">
-        <v>48.45</v>
+        <v>40.77</v>
       </c>
       <c r="J143">
         <v>500141</v>
@@ -6379,22 +6379,22 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144">
-        <v>90008</v>
+        <v>90011</v>
       </c>
       <c r="B144" t="s">
         <v>154</v>
       </c>
       <c r="C144" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D144" t="s">
         <v>250</v>
       </c>
       <c r="E144" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F144" s="1">
-        <v>45985</v>
+        <v>45900</v>
       </c>
       <c r="G144" t="s">
         <v>333</v>
@@ -6403,7 +6403,7 @@
         <v>1</v>
       </c>
       <c r="I144">
-        <v>47.79</v>
+        <v>56.58</v>
       </c>
       <c r="J144">
         <v>500142</v>
@@ -6414,22 +6414,22 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145">
-        <v>90012</v>
+        <v>90001</v>
       </c>
       <c r="B145" t="s">
         <v>155</v>
       </c>
       <c r="C145" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D145" t="s">
         <v>250</v>
       </c>
       <c r="E145" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F145" s="1">
-        <v>45970</v>
+        <v>46070</v>
       </c>
       <c r="G145" t="s">
         <v>333</v>
@@ -6438,7 +6438,7 @@
         <v>1</v>
       </c>
       <c r="I145">
-        <v>22.66</v>
+        <v>28.12</v>
       </c>
       <c r="J145">
         <v>500143</v>
@@ -6455,7 +6455,7 @@
         <v>156</v>
       </c>
       <c r="C146" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D146" t="s">
         <v>250</v>
@@ -6464,7 +6464,7 @@
         <v>255</v>
       </c>
       <c r="F146" s="1">
-        <v>45686</v>
+        <v>46059</v>
       </c>
       <c r="G146" t="s">
         <v>333</v>
@@ -6473,7 +6473,7 @@
         <v>1</v>
       </c>
       <c r="I146">
-        <v>30.33</v>
+        <v>13.62</v>
       </c>
       <c r="J146">
         <v>500144</v>
@@ -6484,22 +6484,22 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147">
-        <v>90008</v>
+        <v>90004</v>
       </c>
       <c r="B147" t="s">
         <v>157</v>
       </c>
       <c r="C147" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D147" t="s">
         <v>250</v>
       </c>
       <c r="E147" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F147" s="1">
-        <v>46033</v>
+        <v>46025</v>
       </c>
       <c r="G147" t="s">
         <v>333</v>
@@ -6508,7 +6508,7 @@
         <v>1</v>
       </c>
       <c r="I147">
-        <v>59.39</v>
+        <v>28.06</v>
       </c>
       <c r="J147">
         <v>500145</v>
@@ -6519,22 +6519,22 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148">
-        <v>90009</v>
+        <v>90006</v>
       </c>
       <c r="B148" t="s">
         <v>158</v>
       </c>
       <c r="C148" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D148" t="s">
         <v>250</v>
       </c>
       <c r="E148" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F148" s="1">
-        <v>45983</v>
+        <v>45914</v>
       </c>
       <c r="G148" t="s">
         <v>333</v>
@@ -6543,7 +6543,7 @@
         <v>1</v>
       </c>
       <c r="I148">
-        <v>23.18</v>
+        <v>28.61</v>
       </c>
       <c r="J148">
         <v>500146</v>
@@ -6554,22 +6554,22 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149">
-        <v>90005</v>
+        <v>90003</v>
       </c>
       <c r="B149" t="s">
         <v>159</v>
       </c>
       <c r="C149" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D149" t="s">
         <v>250</v>
       </c>
       <c r="E149" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F149" s="1">
-        <v>45729</v>
+        <v>45779</v>
       </c>
       <c r="G149" t="s">
         <v>333</v>
@@ -6578,7 +6578,7 @@
         <v>1</v>
       </c>
       <c r="I149">
-        <v>54.72</v>
+        <v>57.49</v>
       </c>
       <c r="J149">
         <v>500147</v>
@@ -6589,7 +6589,7 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150">
-        <v>90003</v>
+        <v>90011</v>
       </c>
       <c r="B150" t="s">
         <v>160</v>
@@ -6601,10 +6601,10 @@
         <v>250</v>
       </c>
       <c r="E150" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F150" s="1">
-        <v>45997</v>
+        <v>45809</v>
       </c>
       <c r="G150" t="s">
         <v>333</v>
@@ -6613,7 +6613,7 @@
         <v>1</v>
       </c>
       <c r="I150">
-        <v>11.73</v>
+        <v>19.08</v>
       </c>
       <c r="J150">
         <v>500148</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151">
-        <v>90006</v>
+        <v>90010</v>
       </c>
       <c r="B151" t="s">
         <v>161</v>
       </c>
       <c r="C151" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D151" t="s">
         <v>250</v>
       </c>
       <c r="E151" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F151" s="1">
-        <v>45761</v>
+        <v>45980</v>
       </c>
       <c r="G151" t="s">
         <v>333</v>
@@ -6648,7 +6648,7 @@
         <v>1</v>
       </c>
       <c r="I151">
-        <v>57.56</v>
+        <v>58.13</v>
       </c>
       <c r="J151">
         <v>500149</v>
@@ -6659,13 +6659,13 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152">
-        <v>90011</v>
+        <v>90006</v>
       </c>
       <c r="B152" t="s">
         <v>162</v>
       </c>
       <c r="C152" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D152" t="s">
         <v>250</v>
@@ -6674,7 +6674,7 @@
         <v>255</v>
       </c>
       <c r="F152" s="1">
-        <v>45857</v>
+        <v>45693</v>
       </c>
       <c r="G152" t="s">
         <v>333</v>
@@ -6683,7 +6683,7 @@
         <v>1</v>
       </c>
       <c r="I152">
-        <v>30.14</v>
+        <v>40.35</v>
       </c>
       <c r="J152">
         <v>500150</v>
@@ -6694,13 +6694,13 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153">
-        <v>90005</v>
+        <v>90006</v>
       </c>
       <c r="B153" t="s">
         <v>163</v>
       </c>
       <c r="C153" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D153" t="s">
         <v>250</v>
@@ -6709,7 +6709,7 @@
         <v>255</v>
       </c>
       <c r="F153" s="1">
-        <v>45766</v>
+        <v>45925</v>
       </c>
       <c r="G153" t="s">
         <v>333</v>
@@ -6718,7 +6718,7 @@
         <v>1</v>
       </c>
       <c r="I153">
-        <v>23.48</v>
+        <v>52.75</v>
       </c>
       <c r="J153">
         <v>500151</v>
@@ -6729,22 +6729,22 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154">
-        <v>90007</v>
+        <v>90001</v>
       </c>
       <c r="B154" t="s">
         <v>164</v>
       </c>
       <c r="C154" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D154" t="s">
         <v>250</v>
       </c>
       <c r="E154" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F154" s="1">
-        <v>46132</v>
+        <v>45737</v>
       </c>
       <c r="G154" t="s">
         <v>333</v>
@@ -6753,7 +6753,7 @@
         <v>1</v>
       </c>
       <c r="I154">
-        <v>33.24</v>
+        <v>13.87</v>
       </c>
       <c r="J154">
         <v>500152</v>
@@ -6764,22 +6764,22 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155">
-        <v>90001</v>
+        <v>90011</v>
       </c>
       <c r="B155" t="s">
         <v>165</v>
       </c>
       <c r="C155" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D155" t="s">
         <v>250</v>
       </c>
       <c r="E155" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F155" s="1">
-        <v>45681</v>
+        <v>45821</v>
       </c>
       <c r="G155" t="s">
         <v>333</v>
@@ -6788,7 +6788,7 @@
         <v>1</v>
       </c>
       <c r="I155">
-        <v>36.15</v>
+        <v>56.48</v>
       </c>
       <c r="J155">
         <v>500153</v>
@@ -6799,22 +6799,22 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156">
-        <v>90009</v>
+        <v>90006</v>
       </c>
       <c r="B156" t="s">
         <v>166</v>
       </c>
       <c r="C156" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="D156" t="s">
         <v>250</v>
       </c>
       <c r="E156" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F156" s="1">
-        <v>45930</v>
+        <v>45875</v>
       </c>
       <c r="G156" t="s">
         <v>333</v>
@@ -6823,7 +6823,7 @@
         <v>1</v>
       </c>
       <c r="I156">
-        <v>46.4</v>
+        <v>44.97</v>
       </c>
       <c r="J156">
         <v>500154</v>
@@ -6834,22 +6834,22 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157">
-        <v>90002</v>
+        <v>90007</v>
       </c>
       <c r="B157" t="s">
         <v>167</v>
       </c>
       <c r="C157" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D157" t="s">
         <v>250</v>
       </c>
       <c r="E157" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F157" s="1">
-        <v>45956</v>
+        <v>45669</v>
       </c>
       <c r="G157" t="s">
         <v>333</v>
@@ -6858,7 +6858,7 @@
         <v>1</v>
       </c>
       <c r="I157">
-        <v>10.91</v>
+        <v>19.27</v>
       </c>
       <c r="J157">
         <v>500155</v>
@@ -6869,22 +6869,22 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158">
-        <v>90004</v>
+        <v>90003</v>
       </c>
       <c r="B158" t="s">
         <v>168</v>
       </c>
       <c r="C158" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D158" t="s">
         <v>250</v>
       </c>
       <c r="E158" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F158" s="1">
-        <v>46020</v>
+        <v>45984</v>
       </c>
       <c r="G158" t="s">
         <v>333</v>
@@ -6893,7 +6893,7 @@
         <v>1</v>
       </c>
       <c r="I158">
-        <v>38.87</v>
+        <v>56.26</v>
       </c>
       <c r="J158">
         <v>500156</v>
@@ -6904,13 +6904,13 @@
     </row>
     <row r="159" spans="1:12">
       <c r="A159">
-        <v>90008</v>
+        <v>90011</v>
       </c>
       <c r="B159" t="s">
         <v>169</v>
       </c>
       <c r="C159" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D159" t="s">
         <v>250</v>
@@ -6919,7 +6919,7 @@
         <v>255</v>
       </c>
       <c r="F159" s="1">
-        <v>45897</v>
+        <v>45665</v>
       </c>
       <c r="G159" t="s">
         <v>333</v>
@@ -6928,7 +6928,7 @@
         <v>1</v>
       </c>
       <c r="I159">
-        <v>33.31</v>
+        <v>10.18</v>
       </c>
       <c r="J159">
         <v>500157</v>
@@ -6945,16 +6945,16 @@
         <v>170</v>
       </c>
       <c r="C160" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D160" t="s">
         <v>250</v>
       </c>
       <c r="E160" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F160" s="1">
-        <v>46007</v>
+        <v>45989</v>
       </c>
       <c r="G160" t="s">
         <v>333</v>
@@ -6963,7 +6963,7 @@
         <v>1</v>
       </c>
       <c r="I160">
-        <v>53.92</v>
+        <v>58.92</v>
       </c>
       <c r="J160">
         <v>500158</v>
@@ -6974,22 +6974,22 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161">
-        <v>90008</v>
+        <v>90002</v>
       </c>
       <c r="B161" t="s">
         <v>171</v>
       </c>
       <c r="C161" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D161" t="s">
         <v>250</v>
       </c>
       <c r="E161" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F161" s="1">
-        <v>45787</v>
+        <v>46041</v>
       </c>
       <c r="G161" t="s">
         <v>333</v>
@@ -6998,7 +6998,7 @@
         <v>1</v>
       </c>
       <c r="I161">
-        <v>29.25</v>
+        <v>51.59</v>
       </c>
       <c r="J161">
         <v>500159</v>
